--- a/Project_ETF/ETF_Investment_Portfolio/00981A/ETF_Investment_Portfolio_20260807.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00981A/ETF_Investment_Portfolio_20260807.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D75"/>
+  <dimension ref="A1:D74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>9.28%</t>
+          <t>9.63%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>8.34%</t>
+          <t>8.53%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>6.90%</t>
+          <t>7.11%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>6.36%</t>
+          <t>6.46%</t>
         </is>
       </c>
     </row>
@@ -704,95 +704,95 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.55%</t>
+          <t>5.75%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>5,801,000</t>
+          <t>2,708,000</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>5.51%</t>
+          <t>5.53%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>2,708,000</t>
+          <t>5,801,000</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>5.49%</t>
+          <t>5.41%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>6,419,000</t>
+          <t>2,443,000</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>5.00%</t>
+          <t>4.99%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>2,443,000</t>
+          <t>6,419,000</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>4.98%</t>
+          <t>4.76%</t>
         </is>
       </c>
     </row>
@@ -814,90 +814,90 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>4.69%</t>
+          <t>4.60%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>5,130,848</t>
+          <t>6,706,000</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>3.93%</t>
+          <t>3.70%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>6,505,000</t>
+          <t>2,375,000</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>3.53%</t>
+          <t>3.48%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>87,718,000</t>
+          <t>9,519,000</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>3.45%</t>
+          <t>3.44%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>2,375,000</t>
+          <t>17,439,000</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -909,44 +909,44 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>9,519,000</t>
+          <t>87,718,000</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>3.40%</t>
+          <t>3.41%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>17,439,000</t>
+          <t>4,616,848</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>3.35%</t>
+          <t>3.40%</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.72%</t>
+          <t>2.65%</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2.46%</t>
+          <t>2.49%</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.59%</t>
+          <t>1.64%</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.17%</t>
+          <t>1.15%</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>0.93%</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>0.91%</t>
+          <t>0.92%</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>0.51%</t>
+          <t>0.50%</t>
         </is>
       </c>
     </row>
@@ -1117,12 +1117,12 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>472,000</t>
+          <t>572,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.39%</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.31%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.26%</t>
+          <t>0.27%</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.26%</t>
+          <t>0.25%</t>
         </is>
       </c>
     </row>
@@ -1305,39 +1305,39 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2049</t>
+          <t>6191</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>上銀</t>
+          <t>精成科</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>1,080,000</t>
+          <t>3,988,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.13%</t>
+          <t>0.11%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>6191</t>
+          <t>3376</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>精成科</t>
+          <t>新日興</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>3,988,000</t>
+          <t>1,741,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -1349,83 +1349,83 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>3376</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>新日興</t>
+          <t>欣銓</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>1,741,000</t>
+          <t>1,508,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.11%</t>
+          <t>0.10%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>欣銓</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>1,508,000</t>
+          <t>23,000</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.10%</t>
+          <t>0.05%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>譜瑞-KY</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>23,000</t>
+          <t>140,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.05%</t>
+          <t>0.03%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>譜瑞-KY</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>140,000</t>
+          <t>5,163,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1437,34 +1437,34 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>8358</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>5,163,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>0.03%</t>
+          <t>0.00%</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -1481,12 +1481,12 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>世界</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -1503,12 +1503,12 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>2439</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>美律</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -1525,17 +1525,17 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2481</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>強茂</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>5,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -1547,12 +1547,12 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -1569,12 +1569,12 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -1591,12 +1591,12 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>世界</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -1613,12 +1613,12 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>嘉澤</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -1635,12 +1635,12 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>嘉澤</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -1657,17 +1657,17 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2481</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>強茂</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>5,000</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -1679,12 +1679,12 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -1701,12 +1701,12 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>8358</t>
+          <t>2439</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>美律</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
@@ -1723,39 +1723,35 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>C_NTD</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>1,000</t>
-        </is>
-      </c>
-      <c r="D72" s="4" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
+          <t>18,314,239,808</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>C_NTD</t>
+          <t>M_NTD</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>MARGIN</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>26,086,970,077</t>
+          <t>4,403,648,006</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr"/>
@@ -1763,38 +1759,20 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>M_NTD</t>
+          <t>RDI_NTD</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>MARGIN</t>
+          <t>RECEIVABLES FOR DISPOSAL OF INVESTMENTS</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>4,388,516,006</t>
+          <t>605,031,529</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="3" t="inlineStr">
-        <is>
-          <t>RDI_NTD</t>
-        </is>
-      </c>
-      <c r="B75" s="3" t="inlineStr">
-        <is>
-          <t>RECEIVABLES FOR DISPOSAL OF INVESTMENTS</t>
-        </is>
-      </c>
-      <c r="C75" s="4" t="inlineStr">
-        <is>
-          <t>48,814,018</t>
-        </is>
-      </c>
-      <c r="D75" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="5">
